--- a/Deliverables/BOM/LCSC-BOM.xlsx
+++ b/Deliverables/BOM/LCSC-BOM.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49863034-2F07-4634-B50F-B40940A55763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D4F0E50A-C57A-4E56-80D6-C3E94E5D1AEE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -137,7 +136,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -684,7 +683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2990240D-2E4D-4C3B-B27C-98B62FAFA8BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:D32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -971,7 +970,7 @@
     </row>
     <row r="27" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>25</v>
@@ -982,7 +981,7 @@
     </row>
     <row r="28" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>26</v>
@@ -993,7 +992,7 @@
     </row>
     <row r="29" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>27</v>
@@ -1004,7 +1003,7 @@
     </row>
     <row r="30" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>28</v>
@@ -1015,7 +1014,7 @@
     </row>
     <row r="31" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>29</v>
@@ -1026,7 +1025,7 @@
     </row>
     <row r="32" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>30</v>

--- a/Deliverables/BOM/LCSC-BOM.xlsx
+++ b/Deliverables/BOM/LCSC-BOM.xlsx
@@ -1,38 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B35E73-8487-484F-9BC3-447A66DCE064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="10 Boards" sheetId="1" r:id="rId1"/>
+    <sheet name="25 Boards" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t xml:space="preserve"> LCSC/Part Number</t>
   </si>
@@ -97,9 +91,6 @@
     <t>C98220</t>
   </si>
   <si>
-    <t>C114630</t>
-  </si>
-  <si>
     <t>C103893</t>
   </si>
   <si>
@@ -131,13 +122,19 @@
   </si>
   <si>
     <t>S. NO</t>
+  </si>
+  <si>
+    <t>C22548</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MOQ (10 Boards)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,13 +152,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF333333"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -228,10 +218,12 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -241,10 +233,25 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -259,17 +266,19 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -281,25 +290,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -314,61 +308,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -683,7 +665,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:D32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -695,342 +677,699 @@
     <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>4</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>6</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>7</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>8</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>9</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>10</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>11</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>13</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>14</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>15</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>16</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>17</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>18</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>19</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>20</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>21</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>22</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>23</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>24</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>25</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>26</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>27</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>28</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <v>29</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="2">
+        <v>30</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="14">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFB5F2B2-53BF-4E56-9496-EF0D589D950B}">
+  <dimension ref="B1:D32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="12">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="8">
         <v>200</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="12">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="12">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="4">
         <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="12">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="12">
+      <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="4">
         <v>60</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="12">
+      <c r="B8" s="2">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="12">
+      <c r="B9" s="2">
         <v>7</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="4">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="12">
+      <c r="B10" s="2">
         <v>8</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="5">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="12">
+      <c r="B11" s="2">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="4">
         <v>60</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="12">
+      <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="3">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="12">
+      <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="4">
         <v>28</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="12">
+      <c r="B14" s="2">
         <v>12</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="3">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="12">
+      <c r="B15" s="2">
         <v>13</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="4">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="12">
+      <c r="B16" s="2">
         <v>14</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="3">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="12">
+      <c r="B17" s="2">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="4">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="12">
+      <c r="B18" s="2">
         <v>16</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="3">
         <v>160</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="12">
+      <c r="B19" s="2">
         <v>17</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="4">
         <v>60</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="12">
+      <c r="B20" s="2">
         <v>18</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="3">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="12">
+      <c r="B21" s="2">
         <v>19</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="4">
         <v>300</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="12">
+      <c r="B22" s="2">
         <v>20</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>21</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D23" s="4">
         <v>400</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="12">
+    <row r="24" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>22</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="D24" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>23</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>24</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="12">
-        <v>22</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="12">
-        <v>23</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="15">
+    <row r="27" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>25</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="4">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="12">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="12">
+    <row r="28" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>26</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="D28" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>27</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
         <v>28</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="12">
-        <v>26</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C30" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="12">
+      <c r="D30" s="3">
         <v>27</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="14">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="12">
+    </row>
+    <row r="31" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <v>29</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="15">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="12">
+      <c r="D31" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="2">
+        <v>30</v>
+      </c>
+      <c r="C32" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="14">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="12">
-        <v>30</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="18">
+      <c r="D32" s="6">
         <v>30</v>
       </c>
     </row>
